--- a/basedatos_partidas/salida/descompuestos/CT-08-05-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-05-020.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 08 Pisos y pavimentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Pisos vinílicos y flexibles</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>

--- a/basedatos_partidas/salida/descompuestos/CT-08-05-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-05-020.xlsx
@@ -654,7 +654,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MO-OF1-SOL</t>
+          <t>MO-OF1-PISO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Oficial de 1ª solador.</t>
+          <t>Oficial de 1ª colocador de pisos.</t>
         </is>
       </c>
       <c r="F17" t="n">
